--- a/China NEA/raw_tables_xlsx/2026-02-21_2025年光伏发电建设情况---国家能源局_raw.xlsx
+++ b/China NEA/raw_tables_xlsx/2026-02-21_2025年光伏发电建设情况---国家能源局_raw.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="299">
-  <si>
-    <t>省(区、市)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="287">
   <si>
     <t>总计</t>
   </si>
@@ -211,19 +208,6 @@
     <t>3415.4</t>
   </si>
   <si>
-    <t>2025年新增并网容量</t>
-  </si>
-  <si>
-    <t>其中：
-集中式</t>
-  </si>
-  <si>
-    <t>光伏电</t>
-  </si>
-  <si>
-    <t>站</t>
-  </si>
-  <si>
     <t>16357.0</t>
   </si>
   <si>
@@ -320,9 +304,6 @@
     <t>3402.1</t>
   </si>
   <si>
-    <t>其中：分布式光伏</t>
-  </si>
-  <si>
     <t>15300.3</t>
   </si>
   <si>
@@ -419,15 +400,6 @@
     <t>13.3</t>
   </si>
   <si>
-    <t>其中：</t>
-  </si>
-  <si>
-    <t>户用光</t>
-  </si>
-  <si>
-    <t>伏</t>
-  </si>
-  <si>
     <t>4594.7</t>
   </si>
   <si>
@@ -524,9 +496,6 @@
     <t>1.7</t>
   </si>
   <si>
-    <t>截至2025年底累计并网容量</t>
-  </si>
-  <si>
     <t>119991.4</t>
   </si>
   <si>
@@ -813,12 +782,6 @@
   </si>
   <si>
     <t>40.1</t>
-  </si>
-  <si>
-    <t>其中：户</t>
-  </si>
-  <si>
-    <t>用光伏</t>
   </si>
   <si>
     <t>20583.2</t>
@@ -918,16 +881,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -943,7 +898,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -951,30 +906,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1269,1166 +1206,935 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="B1" s="1">
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1">
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1" t="s">
+        <v>224</v>
+      </c>
+      <c r="I1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1">
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H2" t="s">
+        <v>225</v>
+      </c>
+      <c r="I2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1">
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1">
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H4" t="s">
+        <v>227</v>
+      </c>
+      <c r="I4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1">
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" t="s">
+        <v>228</v>
+      </c>
+      <c r="I5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1">
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G6" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" t="s">
+        <v>229</v>
+      </c>
+      <c r="I6" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" t="s">
+        <v>199</v>
+      </c>
+      <c r="H8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G9" t="s">
+        <v>200</v>
+      </c>
+      <c r="H9" t="s">
+        <v>232</v>
+      </c>
+      <c r="I9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" t="s">
         <v>169</v>
       </c>
-      <c r="H2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H5" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="G10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H10" t="s">
+        <v>233</v>
+      </c>
+      <c r="I10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G11" t="s">
+        <v>202</v>
+      </c>
+      <c r="H11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I11" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" t="s">
+        <v>171</v>
+      </c>
+      <c r="G12" t="s">
+        <v>203</v>
+      </c>
+      <c r="H12" t="s">
+        <v>235</v>
+      </c>
+      <c r="I12" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" t="s">
-        <v>202</v>
-      </c>
-      <c r="I7" t="s">
-        <v>234</v>
-      </c>
-      <c r="J7" t="s">
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" t="s">
+        <v>172</v>
+      </c>
+      <c r="G13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H13" t="s">
+        <v>236</v>
+      </c>
+      <c r="I13" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" t="s">
-        <v>203</v>
-      </c>
-      <c r="I8" t="s">
-        <v>235</v>
-      </c>
-      <c r="J8" t="s">
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G14" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" t="s">
+        <v>237</v>
+      </c>
+      <c r="I14" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9" t="s">
-        <v>172</v>
-      </c>
-      <c r="H9" t="s">
-        <v>204</v>
-      </c>
-      <c r="I9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" t="s">
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>142</v>
+      </c>
+      <c r="F15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" t="s">
+        <v>206</v>
+      </c>
+      <c r="H15" t="s">
+        <v>238</v>
+      </c>
+      <c r="I15" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G10" t="s">
-        <v>173</v>
-      </c>
-      <c r="H10" t="s">
-        <v>205</v>
-      </c>
-      <c r="I10" t="s">
-        <v>237</v>
-      </c>
-      <c r="J10" t="s">
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>143</v>
+      </c>
+      <c r="F16" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" t="s">
+        <v>207</v>
+      </c>
+      <c r="H16" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" t="s">
-        <v>141</v>
-      </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
-        <v>206</v>
-      </c>
-      <c r="I11" t="s">
-        <v>238</v>
-      </c>
-      <c r="J11" t="s">
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G17" t="s">
+        <v>208</v>
+      </c>
+      <c r="H17" t="s">
+        <v>240</v>
+      </c>
+      <c r="I17" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" t="s">
-        <v>142</v>
-      </c>
-      <c r="G12" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" t="s">
-        <v>207</v>
-      </c>
-      <c r="I12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" t="s">
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" t="s">
+        <v>209</v>
+      </c>
+      <c r="H18" t="s">
+        <v>241</v>
+      </c>
+      <c r="I18" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" t="s">
-        <v>143</v>
-      </c>
-      <c r="G13" t="s">
-        <v>176</v>
-      </c>
-      <c r="H13" t="s">
-        <v>208</v>
-      </c>
-      <c r="I13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J13" t="s">
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" t="s">
+        <v>210</v>
+      </c>
+      <c r="H19" t="s">
+        <v>242</v>
+      </c>
+      <c r="I19" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>109</v>
-      </c>
-      <c r="F14" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" t="s">
-        <v>177</v>
-      </c>
-      <c r="H14" t="s">
-        <v>209</v>
-      </c>
-      <c r="I14" t="s">
-        <v>241</v>
-      </c>
-      <c r="J14" t="s">
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" t="s">
+        <v>179</v>
+      </c>
+      <c r="G20" t="s">
+        <v>211</v>
+      </c>
+      <c r="H20" t="s">
+        <v>243</v>
+      </c>
+      <c r="I20" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" t="s">
-        <v>110</v>
-      </c>
-      <c r="F15" t="s">
-        <v>145</v>
-      </c>
-      <c r="G15" t="s">
-        <v>178</v>
-      </c>
-      <c r="H15" t="s">
-        <v>210</v>
-      </c>
-      <c r="I15" t="s">
-        <v>242</v>
-      </c>
-      <c r="J15" t="s">
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" t="s">
+        <v>180</v>
+      </c>
+      <c r="G21" t="s">
+        <v>212</v>
+      </c>
+      <c r="H21" t="s">
+        <v>244</v>
+      </c>
+      <c r="I21" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" t="s">
-        <v>111</v>
-      </c>
-      <c r="F16" t="s">
-        <v>146</v>
-      </c>
-      <c r="G16" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" t="s">
-        <v>211</v>
-      </c>
-      <c r="I16" t="s">
-        <v>243</v>
-      </c>
-      <c r="J16" t="s">
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22" t="s">
+        <v>181</v>
+      </c>
+      <c r="G22" t="s">
+        <v>213</v>
+      </c>
+      <c r="H22" t="s">
+        <v>245</v>
+      </c>
+      <c r="I22" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F17" t="s">
-        <v>147</v>
-      </c>
-      <c r="G17" t="s">
-        <v>180</v>
-      </c>
-      <c r="H17" t="s">
-        <v>212</v>
-      </c>
-      <c r="I17" t="s">
-        <v>244</v>
-      </c>
-      <c r="J17" t="s">
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" t="s">
+        <v>182</v>
+      </c>
+      <c r="G23" t="s">
+        <v>214</v>
+      </c>
+      <c r="H23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I23" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18" t="s">
-        <v>181</v>
-      </c>
-      <c r="H18" t="s">
-        <v>213</v>
-      </c>
-      <c r="I18" t="s">
-        <v>245</v>
-      </c>
-      <c r="J18" t="s">
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" t="s">
+        <v>183</v>
+      </c>
+      <c r="G24" t="s">
+        <v>215</v>
+      </c>
+      <c r="H24" t="s">
+        <v>247</v>
+      </c>
+      <c r="I24" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" t="s">
-        <v>114</v>
-      </c>
-      <c r="F19" t="s">
-        <v>149</v>
-      </c>
-      <c r="G19" t="s">
-        <v>182</v>
-      </c>
-      <c r="H19" t="s">
-        <v>214</v>
-      </c>
-      <c r="I19" t="s">
-        <v>246</v>
-      </c>
-      <c r="J19" t="s">
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" t="s">
+        <v>184</v>
+      </c>
+      <c r="G25" t="s">
+        <v>216</v>
+      </c>
+      <c r="H25" t="s">
+        <v>248</v>
+      </c>
+      <c r="I25" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G20" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" t="s">
-        <v>215</v>
-      </c>
-      <c r="I20" t="s">
-        <v>247</v>
-      </c>
-      <c r="J20" t="s">
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F26" t="s">
+        <v>185</v>
+      </c>
+      <c r="G26" t="s">
+        <v>217</v>
+      </c>
+      <c r="H26" t="s">
+        <v>249</v>
+      </c>
+      <c r="I26" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" t="s">
-        <v>151</v>
-      </c>
-      <c r="G21" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" t="s">
-        <v>216</v>
-      </c>
-      <c r="I21" t="s">
-        <v>248</v>
-      </c>
-      <c r="J21" t="s">
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" t="s">
+        <v>218</v>
+      </c>
+      <c r="H27" t="s">
+        <v>250</v>
+      </c>
+      <c r="I27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F28" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" t="s">
+        <v>219</v>
+      </c>
+      <c r="H28" t="s">
+        <v>251</v>
+      </c>
+      <c r="I28" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" t="s">
-        <v>117</v>
-      </c>
-      <c r="F22" t="s">
-        <v>152</v>
-      </c>
-      <c r="G22" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" t="s">
-        <v>217</v>
-      </c>
-      <c r="I22" t="s">
-        <v>249</v>
-      </c>
-      <c r="J22" t="s">
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" t="s">
+        <v>220</v>
+      </c>
+      <c r="H29" t="s">
+        <v>252</v>
+      </c>
+      <c r="I29" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" t="s">
-        <v>153</v>
-      </c>
-      <c r="G23" t="s">
-        <v>186</v>
-      </c>
-      <c r="H23" t="s">
-        <v>218</v>
-      </c>
-      <c r="I23" t="s">
-        <v>250</v>
-      </c>
-      <c r="J23" t="s">
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D30" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" t="s">
+        <v>221</v>
+      </c>
+      <c r="H30" t="s">
+        <v>253</v>
+      </c>
+      <c r="I30" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="1">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" t="s">
-        <v>154</v>
-      </c>
-      <c r="G24" t="s">
-        <v>187</v>
-      </c>
-      <c r="H24" t="s">
-        <v>219</v>
-      </c>
-      <c r="I24" t="s">
-        <v>251</v>
-      </c>
-      <c r="J24" t="s">
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" t="s">
+        <v>158</v>
+      </c>
+      <c r="F31" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" t="s">
+        <v>222</v>
+      </c>
+      <c r="H31" t="s">
+        <v>254</v>
+      </c>
+      <c r="I31" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" t="s">
-        <v>120</v>
-      </c>
-      <c r="F25" t="s">
-        <v>155</v>
-      </c>
-      <c r="G25" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" t="s">
-        <v>220</v>
-      </c>
-      <c r="I25" t="s">
-        <v>252</v>
-      </c>
-      <c r="J25" t="s">
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E32" t="s">
+        <v>159</v>
+      </c>
+      <c r="F32" t="s">
+        <v>191</v>
+      </c>
+      <c r="G32" t="s">
+        <v>223</v>
+      </c>
+      <c r="H32" t="s">
+        <v>255</v>
+      </c>
+      <c r="I32" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="1">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" t="s">
-        <v>156</v>
-      </c>
-      <c r="G26" t="s">
-        <v>189</v>
-      </c>
-      <c r="H26" t="s">
-        <v>221</v>
-      </c>
-      <c r="I26" t="s">
-        <v>253</v>
-      </c>
-      <c r="J26" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="1">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" t="s">
-        <v>157</v>
-      </c>
-      <c r="G27" t="s">
-        <v>190</v>
-      </c>
-      <c r="H27" t="s">
-        <v>222</v>
-      </c>
-      <c r="I27" t="s">
-        <v>254</v>
-      </c>
-      <c r="J27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" t="s">
-        <v>123</v>
-      </c>
-      <c r="F28" t="s">
-        <v>158</v>
-      </c>
-      <c r="G28" t="s">
-        <v>191</v>
-      </c>
-      <c r="H28" t="s">
-        <v>223</v>
-      </c>
-      <c r="I28" t="s">
-        <v>255</v>
-      </c>
-      <c r="J28" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="1">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" t="s">
-        <v>124</v>
-      </c>
-      <c r="F29" t="s">
-        <v>159</v>
-      </c>
-      <c r="G29" t="s">
-        <v>192</v>
-      </c>
-      <c r="H29" t="s">
-        <v>224</v>
-      </c>
-      <c r="I29" t="s">
-        <v>256</v>
-      </c>
-      <c r="J29" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="1">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" t="s">
-        <v>92</v>
-      </c>
-      <c r="E30" t="s">
-        <v>125</v>
-      </c>
-      <c r="F30" t="s">
-        <v>160</v>
-      </c>
-      <c r="G30" t="s">
-        <v>193</v>
-      </c>
-      <c r="H30" t="s">
-        <v>225</v>
-      </c>
-      <c r="I30" t="s">
-        <v>257</v>
-      </c>
-      <c r="J30" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="1">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F31" t="s">
-        <v>161</v>
-      </c>
-      <c r="G31" t="s">
-        <v>194</v>
-      </c>
-      <c r="H31" t="s">
-        <v>226</v>
-      </c>
-      <c r="I31" t="s">
-        <v>258</v>
-      </c>
-      <c r="J31" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="1">
-        <v>30</v>
-      </c>
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" t="s">
-        <v>127</v>
-      </c>
-      <c r="F32" t="s">
-        <v>162</v>
-      </c>
-      <c r="G32" t="s">
-        <v>195</v>
-      </c>
-      <c r="H32" t="s">
-        <v>227</v>
-      </c>
-      <c r="I32" t="s">
-        <v>259</v>
-      </c>
-      <c r="J32" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F33" t="s">
-        <v>163</v>
-      </c>
-      <c r="G33" t="s">
-        <v>196</v>
-      </c>
-      <c r="H33" t="s">
-        <v>228</v>
-      </c>
-      <c r="I33" t="s">
-        <v>260</v>
-      </c>
-      <c r="J33" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="1">
-        <v>32</v>
-      </c>
-      <c r="B34" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" t="s">
-        <v>60</v>
-      </c>
-      <c r="D34" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F34" t="s">
-        <v>164</v>
-      </c>
-      <c r="G34" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" t="s">
-        <v>229</v>
-      </c>
-      <c r="I34" t="s">
-        <v>261</v>
-      </c>
-      <c r="J34" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="1">
-        <v>33</v>
-      </c>
-      <c r="B35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" t="s">
-        <v>61</v>
-      </c>
-      <c r="D35" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" t="s">
-        <v>130</v>
-      </c>
-      <c r="F35" t="s">
-        <v>165</v>
-      </c>
-      <c r="G35" t="s">
-        <v>198</v>
-      </c>
-      <c r="H35" t="s">
-        <v>230</v>
-      </c>
-      <c r="I35" t="s">
-        <v>262</v>
-      </c>
-      <c r="J35" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="1">
-        <v>34</v>
-      </c>
-      <c r="B36" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D36" t="s">
-        <v>98</v>
-      </c>
-      <c r="E36" t="s">
-        <v>131</v>
-      </c>
-      <c r="F36" t="s">
-        <v>166</v>
-      </c>
-      <c r="G36" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" t="s">
-        <v>231</v>
-      </c>
-      <c r="I36" t="s">
-        <v>263</v>
-      </c>
-      <c r="J36" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="1">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C37" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" t="s">
-        <v>132</v>
-      </c>
-      <c r="F37" t="s">
-        <v>167</v>
-      </c>
-      <c r="G37" t="s">
-        <v>200</v>
-      </c>
-      <c r="H37" t="s">
-        <v>232</v>
-      </c>
-      <c r="I37" t="s">
-        <v>264</v>
-      </c>
-      <c r="J37" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="1">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" t="s">
-        <v>100</v>
-      </c>
-      <c r="E38" t="s">
-        <v>133</v>
-      </c>
-      <c r="F38" t="s">
-        <v>168</v>
-      </c>
-      <c r="G38" t="s">
-        <v>201</v>
-      </c>
-      <c r="H38" t="s">
-        <v>233</v>
-      </c>
-      <c r="I38" t="s">
-        <v>265</v>
-      </c>
-      <c r="J38" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>
